--- a/experiment/SwinT2_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/SwinT2_bestx4/Test/results-Set5/Set5.xlsx
@@ -455,7 +455,7 @@
         <v>33.69</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8932</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.5</v>
+        <v>34.57</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9369</v>
+        <v>0.9376</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.23</v>
+        <v>28.32</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9086</v>
+        <v>0.9104</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.95</v>
+        <v>32.96</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7971</v>
+        <v>0.7975</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.48</v>
+        <v>30.44</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9101</v>
+        <v>0.9104</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.97</v>
+        <v>32</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8892</v>
+        <v>0.8899</v>
       </c>
     </row>
   </sheetData>
